--- a/artfynd/A 46962-2025 artfynd.xlsx
+++ b/artfynd/A 46962-2025 artfynd.xlsx
@@ -782,56 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132785974</v>
+        <v>132785967</v>
       </c>
       <c r="B3" t="n">
-        <v>57953</v>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hästskomyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>736523</v>
+        <v>736550</v>
       </c>
       <c r="R3" t="n">
-        <v>7076560</v>
+        <v>7076519</v>
       </c>
       <c r="S3" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,48 +889,56 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132785967</v>
+        <v>132785974</v>
       </c>
       <c r="B4" t="n">
-        <v>91872</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hästskomyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>736550</v>
+        <v>736523</v>
       </c>
       <c r="R4" t="n">
-        <v>7076519</v>
+        <v>7076560</v>
       </c>
       <c r="S4" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -982,7 +977,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 46962-2025 artfynd.xlsx
+++ b/artfynd/A 46962-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>132785970</v>
       </c>
       <c r="B2" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>132785967</v>
       </c>
       <c r="B3" t="n">
-        <v>91872</v>
+        <v>91873</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>132785974</v>
       </c>
       <c r="B4" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>132785968</v>
       </c>
       <c r="B5" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>132785964</v>
       </c>
       <c r="B6" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>132785971</v>
       </c>
       <c r="B7" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>132785973</v>
       </c>
       <c r="B8" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>132785962</v>
       </c>
       <c r="B9" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>132785977</v>
       </c>
       <c r="B10" t="n">
-        <v>58114</v>
+        <v>58115</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,6 +1703,902 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132876126</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57341</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100091</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Storspov</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Numenius arquata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hästskomyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>736484</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7076618</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132876118</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hästskomyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>736580</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7076655</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132876119</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91910</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hästskomyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>736439</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7076790</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132876122</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92633</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hästskomyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>736379</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7076925</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132876121</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92098</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1588</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Violmussling</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Trichaptum laricinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hästskomyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>736372</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7076923</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132876125</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79360</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>185</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hästskomyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>736477</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7076664</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132876120</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79947</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hästskomyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>736405</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7076922</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132876123</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79352</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hästskomyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>736440</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7076726</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hörnefors</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46962-2025 artfynd.xlsx
+++ b/artfynd/A 46962-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>132785967</v>
       </c>
       <c r="B3" t="n">
-        <v>91873</v>
+        <v>91875</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>132876119</v>
       </c>
       <c r="B13" t="n">
-        <v>91910</v>
+        <v>91912</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>132876122</v>
       </c>
       <c r="B14" t="n">
-        <v>92633</v>
+        <v>92635</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>132876121</v>
       </c>
       <c r="B15" t="n">
-        <v>92098</v>
+        <v>92100</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 46962-2025 artfynd.xlsx
+++ b/artfynd/A 46962-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132785970</v>
       </c>
       <c r="B2" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>132785967</v>
       </c>
       <c r="B3" t="n">
-        <v>91875</v>
+        <v>91876</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>132785962</v>
       </c>
       <c r="B9" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132876118</v>
+        <v>132876119</v>
       </c>
       <c r="B12" t="n">
-        <v>79328</v>
+        <v>91913</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1836,21 +1836,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1864,10 +1864,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>736580</v>
+        <v>736439</v>
       </c>
       <c r="R12" t="n">
-        <v>7076655</v>
+        <v>7076790</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1936,10 +1936,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132876119</v>
+        <v>132876118</v>
       </c>
       <c r="B13" t="n">
-        <v>91912</v>
+        <v>79329</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>736439</v>
+        <v>736580</v>
       </c>
       <c r="R13" t="n">
-        <v>7076790</v>
+        <v>7076655</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2050,7 +2050,7 @@
         <v>132876122</v>
       </c>
       <c r="B14" t="n">
-        <v>92635</v>
+        <v>92636</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>132876121</v>
       </c>
       <c r="B15" t="n">
-        <v>92100</v>
+        <v>92101</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>132876125</v>
       </c>
       <c r="B16" t="n">
-        <v>79360</v>
+        <v>79361</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>132876120</v>
       </c>
       <c r="B17" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>132876123</v>
       </c>
       <c r="B18" t="n">
-        <v>79352</v>
+        <v>79353</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 46962-2025 artfynd.xlsx
+++ b/artfynd/A 46962-2025 artfynd.xlsx
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132876119</v>
+        <v>132876118</v>
       </c>
       <c r="B12" t="n">
-        <v>91913</v>
+        <v>79329</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1836,21 +1836,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1864,10 +1864,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>736439</v>
+        <v>736580</v>
       </c>
       <c r="R12" t="n">
-        <v>7076790</v>
+        <v>7076655</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1936,10 +1936,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132876118</v>
+        <v>132876119</v>
       </c>
       <c r="B13" t="n">
-        <v>79329</v>
+        <v>91913</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>736580</v>
+        <v>736439</v>
       </c>
       <c r="R13" t="n">
-        <v>7076655</v>
+        <v>7076790</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 46962-2025 artfynd.xlsx
+++ b/artfynd/A 46962-2025 artfynd.xlsx
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132876118</v>
+        <v>132876119</v>
       </c>
       <c r="B12" t="n">
-        <v>79329</v>
+        <v>91913</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1836,21 +1836,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1864,10 +1864,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>736580</v>
+        <v>736439</v>
       </c>
       <c r="R12" t="n">
-        <v>7076655</v>
+        <v>7076790</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1936,10 +1936,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132876119</v>
+        <v>132876118</v>
       </c>
       <c r="B13" t="n">
-        <v>91913</v>
+        <v>79329</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>736439</v>
+        <v>736580</v>
       </c>
       <c r="R13" t="n">
-        <v>7076790</v>
+        <v>7076655</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 46962-2025 artfynd.xlsx
+++ b/artfynd/A 46962-2025 artfynd.xlsx
@@ -782,48 +782,56 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132785967</v>
+        <v>132785974</v>
       </c>
       <c r="B3" t="n">
-        <v>91876</v>
+        <v>57954</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hästskomyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>736550</v>
+        <v>736523</v>
       </c>
       <c r="R3" t="n">
-        <v>7076519</v>
+        <v>7076560</v>
       </c>
       <c r="S3" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +870,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,56 +902,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132785974</v>
+        <v>132785967</v>
       </c>
       <c r="B4" t="n">
-        <v>57954</v>
+        <v>91876</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hästskomyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>736523</v>
+        <v>736550</v>
       </c>
       <c r="R4" t="n">
-        <v>7076560</v>
+        <v>7076519</v>
       </c>
       <c r="S4" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,7 +972,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,12 +982,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132876119</v>
+        <v>132876118</v>
       </c>
       <c r="B12" t="n">
-        <v>91913</v>
+        <v>79329</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1836,21 +1836,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1864,10 +1864,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>736439</v>
+        <v>736580</v>
       </c>
       <c r="R12" t="n">
-        <v>7076790</v>
+        <v>7076655</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1936,10 +1936,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132876118</v>
+        <v>132876119</v>
       </c>
       <c r="B13" t="n">
-        <v>79329</v>
+        <v>91913</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>736580</v>
+        <v>736439</v>
       </c>
       <c r="R13" t="n">
-        <v>7076655</v>
+        <v>7076790</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 46962-2025 artfynd.xlsx
+++ b/artfynd/A 46962-2025 artfynd.xlsx
@@ -782,48 +782,56 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132785967</v>
+        <v>132785974</v>
       </c>
       <c r="B3" t="n">
-        <v>91881</v>
+        <v>57958</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hästskomyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>736550</v>
+        <v>736523</v>
       </c>
       <c r="R3" t="n">
-        <v>7076519</v>
+        <v>7076560</v>
       </c>
       <c r="S3" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +870,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,56 +902,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132785974</v>
+        <v>132785967</v>
       </c>
       <c r="B4" t="n">
-        <v>57958</v>
+        <v>91881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hästskomyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>736523</v>
+        <v>736550</v>
       </c>
       <c r="R4" t="n">
-        <v>7076560</v>
+        <v>7076519</v>
       </c>
       <c r="S4" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,7 +972,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,12 +982,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 46962-2025 artfynd.xlsx
+++ b/artfynd/A 46962-2025 artfynd.xlsx
@@ -782,56 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132785974</v>
+        <v>132785967</v>
       </c>
       <c r="B3" t="n">
-        <v>57958</v>
+        <v>91881</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hästskomyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>736523</v>
+        <v>736550</v>
       </c>
       <c r="R3" t="n">
-        <v>7076560</v>
+        <v>7076519</v>
       </c>
       <c r="S3" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,48 +889,56 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132785967</v>
+        <v>132785974</v>
       </c>
       <c r="B4" t="n">
-        <v>91881</v>
+        <v>57958</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hästskomyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>736550</v>
+        <v>736523</v>
       </c>
       <c r="R4" t="n">
-        <v>7076519</v>
+        <v>7076560</v>
       </c>
       <c r="S4" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -982,7 +977,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132876118</v>
+        <v>132876119</v>
       </c>
       <c r="B12" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1836,21 +1836,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1864,10 +1864,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>736580</v>
+        <v>736439</v>
       </c>
       <c r="R12" t="n">
-        <v>7076655</v>
+        <v>7076790</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1936,10 +1936,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132876119</v>
+        <v>132876118</v>
       </c>
       <c r="B13" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>736439</v>
+        <v>736580</v>
       </c>
       <c r="R13" t="n">
-        <v>7076790</v>
+        <v>7076655</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 46962-2025 artfynd.xlsx
+++ b/artfynd/A 46962-2025 artfynd.xlsx
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132876119</v>
+        <v>132876118</v>
       </c>
       <c r="B12" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1836,21 +1836,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1864,10 +1864,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>736439</v>
+        <v>736580</v>
       </c>
       <c r="R12" t="n">
-        <v>7076790</v>
+        <v>7076655</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1936,10 +1936,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132876118</v>
+        <v>132876119</v>
       </c>
       <c r="B13" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>736580</v>
+        <v>736439</v>
       </c>
       <c r="R13" t="n">
-        <v>7076655</v>
+        <v>7076790</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 46962-2025 artfynd.xlsx
+++ b/artfynd/A 46962-2025 artfynd.xlsx
@@ -782,56 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132785974</v>
+        <v>132785967</v>
       </c>
       <c r="B3" t="n">
-        <v>57958</v>
+        <v>91881</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hästskomyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>736523</v>
+        <v>736550</v>
       </c>
       <c r="R3" t="n">
-        <v>7076560</v>
+        <v>7076519</v>
       </c>
       <c r="S3" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,48 +889,56 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132785967</v>
+        <v>132785974</v>
       </c>
       <c r="B4" t="n">
-        <v>91881</v>
+        <v>57958</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hästskomyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>736550</v>
+        <v>736523</v>
       </c>
       <c r="R4" t="n">
-        <v>7076519</v>
+        <v>7076560</v>
       </c>
       <c r="S4" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -982,7 +977,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 46962-2025 artfynd.xlsx
+++ b/artfynd/A 46962-2025 artfynd.xlsx
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132876118</v>
+        <v>132876119</v>
       </c>
       <c r="B12" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1836,21 +1836,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1864,10 +1864,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>736580</v>
+        <v>736439</v>
       </c>
       <c r="R12" t="n">
-        <v>7076655</v>
+        <v>7076790</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1936,10 +1936,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132876119</v>
+        <v>132876118</v>
       </c>
       <c r="B13" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>736439</v>
+        <v>736580</v>
       </c>
       <c r="R13" t="n">
-        <v>7076790</v>
+        <v>7076655</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 46962-2025 artfynd.xlsx
+++ b/artfynd/A 46962-2025 artfynd.xlsx
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132876119</v>
+        <v>132876118</v>
       </c>
       <c r="B12" t="n">
-        <v>91918</v>
+        <v>79334</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1836,21 +1836,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1864,10 +1864,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>736439</v>
+        <v>736580</v>
       </c>
       <c r="R12" t="n">
-        <v>7076790</v>
+        <v>7076655</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1936,10 +1936,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132876118</v>
+        <v>132876119</v>
       </c>
       <c r="B13" t="n">
-        <v>79333</v>
+        <v>91920</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>736580</v>
+        <v>736439</v>
       </c>
       <c r="R13" t="n">
-        <v>7076655</v>
+        <v>7076790</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2050,7 +2050,7 @@
         <v>132876122</v>
       </c>
       <c r="B14" t="n">
-        <v>92641</v>
+        <v>92643</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>132876121</v>
       </c>
       <c r="B15" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>132876125</v>
       </c>
       <c r="B16" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>132876120</v>
       </c>
       <c r="B17" t="n">
-        <v>79952</v>
+        <v>79953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>132876123</v>
       </c>
       <c r="B18" t="n">
-        <v>79357</v>
+        <v>79358</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
